--- a/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
+++ b/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
   <si>
     <t xml:space="preserve">Reseller profit-after-fees calculator 2026</t>
   </si>
@@ -247,7 +247,10 @@
     <t xml:space="preserve">Mercari</t>
   </si>
   <si>
-    <t xml:space="preserve">Flat 10% on item + buyer-paid shipping. The old 2.9% + $0.50 seller processing fee was removed on 6 Jan 2025; buyers now pay a 3.6% Buyer Protection fee instead.</t>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat 10% on item + buyer-paid shipping. The old 2.9% + $0.50 seller processing fee was removed on 6 Jan 2025; buyers now pay a 3.6% Buyer Protection fee instead. NOT in this row: Mercari charges $2.00 to send a standard direct-deposit payout ($3.00 for Instant Pay). That is per payout, not per sale, so it is not a per-item fee - if you cash out once a month it is $2 across every sale that month, and if you cash out per sale it is $2 on each. Nowhere else in this sheet charges you to be paid.</t>
   </si>
   <si>
     <t xml:space="preserve">Depop</t>
@@ -1315,7 +1318,7 @@
       </c>
       <c r="H14" s="16" t="str">
         <f aca="false">Fees!$K$6</f>
-        <v>2026-09-10</v>
+        <v>2026-09-16</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1650,7 +1653,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>73</v>
       </c>
@@ -1682,15 +1685,15 @@
         <v>0</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L6" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>0</v>
@@ -1720,15 +1723,15 @@
         <v>0</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>0.1</v>
@@ -1758,15 +1761,15 @@
         <v>0.8</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L8" s="27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>0.1</v>
@@ -1796,10 +1799,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1833,35 +1836,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>40</v>
@@ -1878,7 +1881,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>66</v>
@@ -2392,7 +2395,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J25" s="29" t="n">
         <f aca="false">SUM(J4:J23)</f>

--- a/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
+++ b/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
   <si>
     <t xml:space="preserve">Reseller profit-after-fees calculator 2026</t>
   </si>
@@ -229,16 +229,19 @@
     <t xml:space="preserve">Y</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final value fee 13.6% of the total (item + buyer-paid shipping + handling + the sales tax eBay collects) plus $0.40 per order, or $0.30 on orders of $10 or less. Most categories; books/media and some others differ. NOT in this row: the 13.6% applies to the first $7,500 of an order and drops to 2.35% above that. This sheet charges 13.6% on the whole amount, so an order over $7,500 is costed slightly pessimistically - if you sell watches, handbags or collectibles at that level, work that one out by hand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poshmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final value fee 13.6% of the total (item + buyer-paid shipping + handling) plus $0.40 per order, or $0.30 on orders of $10 or less. Most categories; books/media and some others differ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poshmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
   </si>
   <si>
     <t xml:space="preserve">Flat $2.95 on sales under $15, otherwise 20% of the sale price. No separate processing fee. The buyer pays shipping directly, so leave 'buyer-paid shipping you receive' at 0.</t>
@@ -1250,7 +1253,7 @@
       </c>
       <c r="H12" s="16" t="str">
         <f aca="false">Fees!$K$4</f>
-        <v>2026-09-10</v>
+        <v>2026-09-18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1577,7 +1580,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>66</v>
       </c>
@@ -1647,15 +1650,15 @@
         <v>0</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" s="23" t="n">
         <v>0.1</v>
@@ -1685,15 +1688,15 @@
         <v>0</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L6" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>0</v>
@@ -1723,15 +1726,15 @@
         <v>0</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>0.1</v>
@@ -1761,15 +1764,15 @@
         <v>0.8</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L8" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>0.1</v>
@@ -1799,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1836,35 +1839,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>40</v>
@@ -1881,7 +1884,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>66</v>
@@ -2395,7 +2398,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J25" s="29" t="n">
         <f aca="false">SUM(J4:J23)</f>

--- a/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
+++ b/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
@@ -241,10 +241,10 @@
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flat $2.95 on sales under $15, otherwise 20% of the sale price. No separate processing fee. The buyer pays shipping directly, so leave 'buyer-paid shipping you receive' at 0.</t>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat $2.95 on sales under $15, otherwise 20% of the item price. No listing fee, no monthly fee, no separate processing fee, and the 20% includes the prepaid shipping label - which is why this row has fee-on-shipping set to N and why you leave 'buyer-paid shipping you receive' at 0: the buyer pays Poshmark for shipping, not you. Poshmark trialled a different structure in 2024 and reverted it after seller pushback, so this row is worth re-checking more often than the others.</t>
   </si>
   <si>
     <t xml:space="preserve">Mercari</t>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H13" s="16" t="str">
         <f aca="false">Fees!$K$5</f>
-        <v>2026-09-10</v>
+        <v>2026-09-20</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1618,7 +1618,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
         <v>70</v>
       </c>

--- a/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
+++ b/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="96">
   <si>
     <t xml:space="preserve">Reseller profit-after-fees calculator 2026</t>
   </si>
@@ -259,13 +259,16 @@
     <t xml:space="preserve">Depop</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No US selling commission since 2024 - it moved to the buyer's side as a marketplace fee, so the item has to carry a higher sticker price to look comparable. What remains on the seller is 3.3% + $0.45 payment processing via Depop Payments, charged on item + shipping + any applicable tax. NOT in this row: an optional Boosted Listing costs 12% on top, on eligible new listings from 23 March 2026 - if you boost, add 12% of the sale yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook Marketplace</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No US selling commission since 2024 - it moved to the buyer. What remains on the seller is 3.3% + $0.45 payment processing, charged on item + shipping + tax. An optional Boosted Listing costs 12% on top if you use one; this row does not include it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook Marketplace</t>
   </si>
   <si>
     <t xml:space="preserve">10% of the buyer's total (item + the shipping you charge + the sales tax Meta collects), minimum $0.80 per order. Raised from 5% / $0.40 on 15 April 2024. Local pickup sales have no selling fee at all - price those with the 'Other' row set to 0%.</t>
@@ -1355,7 +1358,7 @@
       </c>
       <c r="H15" s="16" t="str">
         <f aca="false">Fees!$K$7</f>
-        <v>2026-09-11</v>
+        <v>2026-09-21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1694,7 +1697,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>77</v>
       </c>
@@ -1764,15 +1767,15 @@
         <v>0.8</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L8" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>0.1</v>
@@ -1802,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1839,35 +1842,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>40</v>
@@ -1884,7 +1887,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>66</v>
@@ -2398,7 +2401,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J25" s="29" t="n">
         <f aca="false">SUM(J4:J23)</f>

--- a/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
+++ b/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
@@ -268,7 +268,7 @@
     <t xml:space="preserve">Facebook Marketplace</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-11</t>
+    <t xml:space="preserve">2026-09-22</t>
   </si>
   <si>
     <t xml:space="preserve">10% of the buyer's total (item + the shipping you charge + the sales tax Meta collects), minimum $0.80 per order. Raised from 5% / $0.40 on 15 April 2024. Local pickup sales have no selling fee at all - price those with the 'Other' row set to 0%.</t>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H16" s="16" t="str">
         <f aca="false">Fees!$K$8</f>
-        <v>2026-09-11</v>
+        <v>2026-09-22</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
